--- a/data/trans_orig/IP1022_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP1022_2023-Habitat-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4944</t>
+          <t>4993</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14125</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8209</t>
+          <t>8579</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34537</t>
+          <t>35815</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16267</t>
+          <t>16429</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46833</t>
+          <t>48332</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,76%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>103155</t>
+          <t>102836</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>112336</t>
+          <t>112287</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>105875</t>
+          <t>104597</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>132203</t>
+          <t>131833</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>210860</t>
+          <t>209361</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>241426</t>
+          <t>241264</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,62%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6640</t>
+          <t>6686</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33466</t>
+          <t>33666</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11716</t>
+          <t>12068</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27467</t>
+          <t>28115</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22176</t>
+          <t>22347</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50982</t>
+          <t>53676</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>12,05%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>157046</t>
+          <t>156846</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>183872</t>
+          <t>183826</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>227568</t>
+          <t>226920</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>243319</t>
+          <t>242967</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>394566</t>
+          <t>391872</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>423372</t>
+          <t>423201</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,98%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9060</t>
+          <t>8294</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24085</t>
+          <t>24396</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3697</t>
+          <t>3655</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14461</t>
+          <t>13515</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16092</t>
+          <t>16074</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33006</t>
+          <t>33013</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>165500</t>
+          <t>165189</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>180525</t>
+          <t>181291</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>166589</t>
+          <t>167535</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>177353</t>
+          <t>177395</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>337629</t>
+          <t>337622</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>354543</t>
+          <t>354561</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2182</t>
+          <t>2503</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9848</t>
+          <t>10508</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9563</t>
+          <t>9109</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22737</t>
+          <t>22636</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13887</t>
+          <t>14037</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28761</t>
+          <t>29025</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>157506</t>
+          <t>156846</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>165172</t>
+          <t>164851</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>158501</t>
+          <t>158602</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>171675</t>
+          <t>172129</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>319831</t>
+          <t>319567</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>334705</t>
+          <t>334555</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31503</t>
+          <t>32300</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>62818</t>
+          <t>64667</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45454</t>
+          <t>44031</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>79980</t>
+          <t>78467</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>83732</t>
+          <t>83249</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>130841</t>
+          <t>130132</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>601914</t>
+          <t>600065</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>633229</t>
+          <t>632432</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>677756</t>
+          <t>679269</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>712282</t>
+          <t>713705</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1291627</t>
+          <t>1292336</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1338736</t>
+          <t>1339219</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,15%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP1022_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP1022_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>8741</t>
+          <t>10758</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4993</t>
+          <t>5717</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>17855</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>16699</t>
+          <t>9029</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8579</t>
+          <t>5266</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35815</t>
+          <t>15318</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>25440</t>
+          <t>19788</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16429</t>
+          <t>13533</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48332</t>
+          <t>28310</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>115148</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>108051</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>120189</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>91,46%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>85,82%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>95,46%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>108539</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>102836</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>112287</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>92,55%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>87,68%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>95,74%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>123713</t>
+          <t>112042</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>104597</t>
+          <t>105753</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>131833</t>
+          <t>115805</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>232253</t>
+          <t>227189</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>209361</t>
+          <t>218667</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>241264</t>
+          <t>233444</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>94,52%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>17358</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>11285</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>26704</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7,32%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4,76%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>11,26%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>13987</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6686</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>33666</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>7,34%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,51%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>17,67%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18605</t>
+          <t>9498</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12068</t>
+          <t>5209</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28115</t>
+          <t>15583</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>32593</t>
+          <t>26857</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22347</t>
+          <t>19492</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53676</t>
+          <t>36281</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>8,61%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>219848</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>210502</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>225921</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>92,68%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>88,74%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,24%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>266</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>176525</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>156846</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>183826</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>92,66%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>82,33%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,49%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>236430</t>
+          <t>174915</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>226920</t>
+          <t>168830</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>242967</t>
+          <t>179204</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>412955</t>
+          <t>394762</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>391872</t>
+          <t>385338</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>423201</t>
+          <t>402127</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,38%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7115</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3208</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12991</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4,34%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,96%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7,92%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>15734</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8294</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>24396</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8,3%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,37%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12,87%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7465</t>
+          <t>16269</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3655</t>
+          <t>10286</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13515</t>
+          <t>24600</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>23199</t>
+          <t>23384</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16074</t>
+          <t>16212</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33013</t>
+          <t>32951</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>156856</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>150980</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>160763</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>95,66%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>92,08%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,04%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>205</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>173851</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>165189</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>181291</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>91,7%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>87,13%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>95,63%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>173585</t>
+          <t>139935</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>167535</t>
+          <t>131604</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>177395</t>
+          <t>145918</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>347436</t>
+          <t>296791</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>337622</t>
+          <t>287224</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>354561</t>
+          <t>303963</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>94,94%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>163971</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>163971</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>163971</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>181050</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>181050</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>181050</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>370635</t>
+          <t>320175</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>370635</t>
+          <t>320175</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>370635</t>
+          <t>320175</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>13794</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8679</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>20434</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8,14%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,12%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>12,06%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>5342</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2503</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>10508</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,28%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14858</t>
+          <t>5510</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9109</t>
+          <t>2325</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22636</t>
+          <t>10338</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>20200</t>
+          <t>19304</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14037</t>
+          <t>13035</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29025</t>
+          <t>27334</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>155582</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>148942</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>160697</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>91,86%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>87,94%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,88%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>162012</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>156846</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>164851</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>96,81%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93,72%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,5%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>166380</t>
+          <t>160965</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>158602</t>
+          <t>156137</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>172129</t>
+          <t>164150</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>328392</t>
+          <t>316547</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>319567</t>
+          <t>308517</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>334555</t>
+          <t>322816</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,12%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>239</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>167354</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>167354</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>167354</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>166475</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>166475</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>166475</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>348592</t>
+          <t>335851</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>348592</t>
+          <t>335851</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>348592</t>
+          <t>335851</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>49026</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>38275</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>63224</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7,04%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5,5%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9,08%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>43804</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>32300</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>64667</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>6,59%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,86%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>9,73%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>57628</t>
+          <t>40307</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44031</t>
+          <t>30744</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>78467</t>
+          <t>52096</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>101432</t>
+          <t>89332</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>83249</t>
+          <t>74610</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>130132</t>
+          <t>106578</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>908</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>647434</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>633236</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>658185</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>92,96%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>90,92%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>94,5%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>884</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>620928</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>600065</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>632432</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>93,41%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>90,27%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>95,14%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>908</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>700108</t>
+          <t>587856</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>679269</t>
+          <t>576067</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>713705</t>
+          <t>597419</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1321036</t>
+          <t>1235291</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1292336</t>
+          <t>1218045</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1339219</t>
+          <t>1250013</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,37%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>696460</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>696460</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>696460</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>941</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>664732</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>664732</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>664732</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>757736</t>
+          <t>628163</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>757736</t>
+          <t>628163</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>757736</t>
+          <t>628163</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1422468</t>
+          <t>1324623</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1422468</t>
+          <t>1324623</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1422468</t>
+          <t>1324623</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
